--- a/Nuevos DeepWins/Problem6_HierarchicalXOR/Res/Comparativa_15_Neuronas.xlsx
+++ b/Nuevos DeepWins/Problem6_HierarchicalXOR/Res/Comparativa_15_Neuronas.xlsx
@@ -581,42 +581,42 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.10992</v>
+        <v>0.248733</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>_4_15_1_</t>
+          <t>_4_5_5_5_1_</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1790733486</v>
+        <v>1790733545</v>
       </c>
       <c r="E2" t="n">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="F2" t="n">
         <v>200000</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8434469999999999</v>
+        <v>0.541892</v>
       </c>
       <c r="H2" t="n">
-        <v>0.860148</v>
+        <v>0.496287</v>
       </c>
       <c r="I2" t="n">
-        <v>0.851716</v>
+        <v>0.518088</v>
       </c>
       <c r="J2" t="n">
-        <v>0.122324</v>
+        <v>0.251032</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.489362</v>
       </c>
       <c r="L2" t="n">
-        <v>0.835052</v>
+        <v>0.474227</v>
       </c>
       <c r="M2" t="n">
-        <v>0.822335</v>
+        <v>0.481675</v>
       </c>
       <c r="N2" t="n">
         <v>0.2</v>
@@ -652,23 +652,23 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>_4_15_1_1790733486_12.txt</t>
+          <t>_4_5_5_5_1_1790733545_2.txt</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[5, 5, 5]</t>
         </is>
       </c>
       <c r="Z2" t="n">
         <v>15</v>
       </c>
       <c r="AA2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -682,42 +682,42 @@
         <v>0.1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.249141</v>
+        <v>0.07828499999999999</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_</t>
+          <t>_4_15_1_</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1790733545</v>
+        <v>1790733486</v>
       </c>
       <c r="E3" t="n">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="F3" t="n">
         <v>200000</v>
       </c>
       <c r="G3" t="n">
-        <v>0.529206</v>
+        <v>0.905119</v>
       </c>
       <c r="H3" t="n">
-        <v>0.560644</v>
+        <v>0.897277</v>
       </c>
       <c r="I3" t="n">
-        <v>0.544471</v>
+        <v>0.901181</v>
       </c>
       <c r="J3" t="n">
-        <v>0.251175</v>
+        <v>0.08906699999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5</v>
+        <v>0.854271</v>
       </c>
       <c r="L3" t="n">
-        <v>0.56701</v>
+        <v>0.876289</v>
       </c>
       <c r="M3" t="n">
-        <v>0.531401</v>
+        <v>0.86514</v>
       </c>
       <c r="N3" t="n">
         <v>0.2</v>
@@ -753,28 +753,28 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_1790733545_17.txt</t>
+          <t>_4_15_1_1790733486_2.txt</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>[5, 5, 5]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z3" t="n">
         <v>15</v>
       </c>
       <c r="AA3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
         <v>0.1</v>
       </c>
       <c r="B4" t="n">
-        <v>0.113256</v>
+        <v>0.172735</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -800,25 +800,25 @@
         <v>200000</v>
       </c>
       <c r="G4" t="n">
-        <v>0.833132</v>
+        <v>0.771739</v>
       </c>
       <c r="H4" t="n">
-        <v>0.852723</v>
+        <v>0.70297</v>
       </c>
       <c r="I4" t="n">
-        <v>0.842813</v>
+        <v>0.735751</v>
       </c>
       <c r="J4" t="n">
-        <v>0.123418</v>
+        <v>0.168591</v>
       </c>
       <c r="K4" t="n">
-        <v>0.815385</v>
+        <v>0.779006</v>
       </c>
       <c r="L4" t="n">
-        <v>0.819588</v>
+        <v>0.726804</v>
       </c>
       <c r="M4" t="n">
-        <v>0.817481</v>
+        <v>0.752</v>
       </c>
       <c r="N4" t="n">
         <v>0.2</v>
@@ -854,7 +854,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>_4_15_1_1790733486_16.txt</t>
+          <t>_4_15_1_1790733486_19.txt</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -884,42 +884,42 @@
         <v>0.1</v>
       </c>
       <c r="B5" t="n">
-        <v>0.248733</v>
+        <v>0.094134</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_</t>
+          <t>_4_15_1_</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1790733545</v>
+        <v>1790733486</v>
       </c>
       <c r="E5" t="n">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="F5" t="n">
         <v>200000</v>
       </c>
       <c r="G5" t="n">
-        <v>0.541892</v>
+        <v>0.882872</v>
       </c>
       <c r="H5" t="n">
-        <v>0.496287</v>
+        <v>0.867574</v>
       </c>
       <c r="I5" t="n">
-        <v>0.518088</v>
+        <v>0.875156</v>
       </c>
       <c r="J5" t="n">
-        <v>0.251032</v>
+        <v>0.096939</v>
       </c>
       <c r="K5" t="n">
-        <v>0.489362</v>
+        <v>0.875676</v>
       </c>
       <c r="L5" t="n">
-        <v>0.474227</v>
+        <v>0.835052</v>
       </c>
       <c r="M5" t="n">
-        <v>0.481675</v>
+        <v>0.854881</v>
       </c>
       <c r="N5" t="n">
         <v>0.2</v>
@@ -955,28 +955,28 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_1790733545_2.txt</t>
+          <t>_4_15_1_1790733486_11.txt</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>[5, 5, 5]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z5" t="n">
         <v>15</v>
       </c>
       <c r="AA5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
         <v>0.1</v>
       </c>
       <c r="B6" t="n">
-        <v>0.249334</v>
+        <v>0.24956</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1002,25 +1002,25 @@
         <v>200000</v>
       </c>
       <c r="G6" t="n">
-        <v>0.524176</v>
+        <v>0.517274</v>
       </c>
       <c r="H6" t="n">
-        <v>0.590347</v>
+        <v>0.667079</v>
       </c>
       <c r="I6" t="n">
-        <v>0.555297</v>
+        <v>0.582703</v>
       </c>
       <c r="J6" t="n">
-        <v>0.251574</v>
+        <v>0.25055</v>
       </c>
       <c r="K6" t="n">
-        <v>0.487179</v>
+        <v>0.463878</v>
       </c>
       <c r="L6" t="n">
-        <v>0.587629</v>
+        <v>0.628866</v>
       </c>
       <c r="M6" t="n">
-        <v>0.53271</v>
+        <v>0.533917</v>
       </c>
       <c r="N6" t="n">
         <v>0.2</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_1790733545_0.txt</t>
+          <t>_4_5_5_5_1_1790733545_19.txt</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1086,42 +1086,42 @@
         <v>0.1</v>
       </c>
       <c r="B7" t="n">
-        <v>0.077861</v>
+        <v>0.249295</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>_4_15_1_</t>
+          <t>_4_5_5_5_1_</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1790733486</v>
+        <v>1790733545</v>
       </c>
       <c r="E7" t="n">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="F7" t="n">
         <v>200000</v>
       </c>
       <c r="G7" t="n">
-        <v>0.91</v>
+        <v>0.5252869999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.90099</v>
+        <v>0.565594</v>
       </c>
       <c r="I7" t="n">
-        <v>0.905473</v>
+        <v>0.544696</v>
       </c>
       <c r="J7" t="n">
-        <v>0.084911</v>
+        <v>0.251227</v>
       </c>
       <c r="K7" t="n">
-        <v>0.891753</v>
+        <v>0.502283</v>
       </c>
       <c r="L7" t="n">
-        <v>0.891753</v>
+        <v>0.56701</v>
       </c>
       <c r="M7" t="n">
-        <v>0.891753</v>
+        <v>0.5326880000000001</v>
       </c>
       <c r="N7" t="n">
         <v>0.2</v>
@@ -1157,28 +1157,28 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>_4_15_1_1790733486_10.txt</t>
+          <t>_4_5_5_5_1_1790733545_16.txt</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[5, 5, 5]</t>
         </is>
       </c>
       <c r="Z7" t="n">
         <v>15</v>
       </c>
       <c r="AA7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1187,42 +1187,42 @@
         <v>0.1</v>
       </c>
       <c r="B8" t="n">
-        <v>0.09222</v>
+        <v>0.249141</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>_4_15_1_</t>
+          <t>_4_5_5_5_1_</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1790733486</v>
+        <v>1790733545</v>
       </c>
       <c r="E8" t="n">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="F8" t="n">
         <v>200000</v>
       </c>
       <c r="G8" t="n">
-        <v>0.89196</v>
+        <v>0.529206</v>
       </c>
       <c r="H8" t="n">
-        <v>0.878713</v>
+        <v>0.560644</v>
       </c>
       <c r="I8" t="n">
-        <v>0.885287</v>
+        <v>0.544471</v>
       </c>
       <c r="J8" t="n">
-        <v>0.100506</v>
+        <v>0.251175</v>
       </c>
       <c r="K8" t="n">
-        <v>0.880208</v>
+        <v>0.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.871134</v>
+        <v>0.56701</v>
       </c>
       <c r="M8" t="n">
-        <v>0.875648</v>
+        <v>0.531401</v>
       </c>
       <c r="N8" t="n">
         <v>0.2</v>
@@ -1258,28 +1258,28 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>_4_15_1_1790733486_0.txt</t>
+          <t>_4_5_5_5_1_1790733545_17.txt</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[5, 5, 5]</t>
         </is>
       </c>
       <c r="Z8" t="n">
         <v>15</v>
       </c>
       <c r="AA8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
         <v>0.1</v>
       </c>
       <c r="B9" t="n">
-        <v>0.249067</v>
+        <v>0.249279</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1305,25 +1305,25 @@
         <v>200000</v>
       </c>
       <c r="G9" t="n">
-        <v>0.536829</v>
+        <v>0.54023</v>
       </c>
       <c r="H9" t="n">
-        <v>0.532178</v>
+        <v>0.639852</v>
       </c>
       <c r="I9" t="n">
-        <v>0.534493</v>
+        <v>0.585836</v>
       </c>
       <c r="J9" t="n">
-        <v>0.251247</v>
+        <v>0.251298</v>
       </c>
       <c r="K9" t="n">
-        <v>0.487805</v>
+        <v>0.508475</v>
       </c>
       <c r="L9" t="n">
-        <v>0.515464</v>
+        <v>0.618557</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5012529999999999</v>
+        <v>0.55814</v>
       </c>
       <c r="N9" t="n">
         <v>0.2</v>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_1790733545_9.txt</t>
+          <t>_4_5_5_5_1_1790733545_13.txt</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1389,7 +1389,7 @@
         <v>0.1</v>
       </c>
       <c r="B10" t="n">
-        <v>0.09510200000000001</v>
+        <v>0.086337</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
         <v>200000</v>
       </c>
       <c r="G10" t="n">
-        <v>0.881841</v>
+        <v>0.922179</v>
       </c>
       <c r="H10" t="n">
-        <v>0.877475</v>
+        <v>0.879951</v>
       </c>
       <c r="I10" t="n">
-        <v>0.879653</v>
+        <v>0.90057</v>
       </c>
       <c r="J10" t="n">
-        <v>0.104068</v>
+        <v>0.084504</v>
       </c>
       <c r="K10" t="n">
-        <v>0.854167</v>
+        <v>0.9297299999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>0.845361</v>
+        <v>0.886598</v>
       </c>
       <c r="M10" t="n">
-        <v>0.849741</v>
+        <v>0.907652</v>
       </c>
       <c r="N10" t="n">
         <v>0.2</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>_4_15_1_1790733486_17.txt</t>
+          <t>_4_15_1_1790733486_6.txt</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1490,42 +1490,42 @@
         <v>0.1</v>
       </c>
       <c r="B11" t="n">
-        <v>0.115343</v>
+        <v>0.249067</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>_4_15_1_</t>
+          <t>_4_5_5_5_1_</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1790733486</v>
+        <v>1790733545</v>
       </c>
       <c r="E11" t="n">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="F11" t="n">
         <v>200000</v>
       </c>
       <c r="G11" t="n">
-        <v>0.834741</v>
+        <v>0.536829</v>
       </c>
       <c r="H11" t="n">
-        <v>0.856436</v>
+        <v>0.532178</v>
       </c>
       <c r="I11" t="n">
-        <v>0.845449</v>
+        <v>0.534493</v>
       </c>
       <c r="J11" t="n">
-        <v>0.124832</v>
+        <v>0.251247</v>
       </c>
       <c r="K11" t="n">
-        <v>0.787129</v>
+        <v>0.487805</v>
       </c>
       <c r="L11" t="n">
-        <v>0.819588</v>
+        <v>0.515464</v>
       </c>
       <c r="M11" t="n">
-        <v>0.80303</v>
+        <v>0.5012529999999999</v>
       </c>
       <c r="N11" t="n">
         <v>0.2</v>
@@ -1561,23 +1561,23 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>_4_15_1_1790733486_8.txt</t>
+          <t>_4_5_5_5_1_1790733545_9.txt</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[5, 5, 5]</t>
         </is>
       </c>
       <c r="Z11" t="n">
         <v>15</v>
       </c>
       <c r="AA11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1591,42 +1591,42 @@
         <v>0.1</v>
       </c>
       <c r="B12" t="n">
-        <v>0.110606</v>
+        <v>0.24934</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>_4_15_1_</t>
+          <t>_4_5_5_5_1_</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1790733486</v>
+        <v>1790733545</v>
       </c>
       <c r="E12" t="n">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="F12" t="n">
         <v>200000</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8394160000000001</v>
+        <v>0.521542</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8539600000000001</v>
+        <v>0.569307</v>
       </c>
       <c r="I12" t="n">
-        <v>0.846626</v>
+        <v>0.5443789999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>0.125746</v>
+        <v>0.251394</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8138300000000001</v>
+        <v>0.482456</v>
       </c>
       <c r="L12" t="n">
-        <v>0.78866</v>
+        <v>0.56701</v>
       </c>
       <c r="M12" t="n">
-        <v>0.801047</v>
+        <v>0.521327</v>
       </c>
       <c r="N12" t="n">
         <v>0.2</v>
@@ -1662,23 +1662,23 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>_4_15_1_1790733486_4.txt</t>
+          <t>_4_5_5_5_1_1790733545_12.txt</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[5, 5, 5]</t>
         </is>
       </c>
       <c r="Z12" t="n">
         <v>15</v>
       </c>
       <c r="AA12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1692,42 +1692,42 @@
         <v>0.1</v>
       </c>
       <c r="B13" t="n">
-        <v>0.094134</v>
+        <v>0.249276</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>_4_15_1_</t>
+          <t>_4_5_5_5_1_</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1790733486</v>
+        <v>1790733545</v>
       </c>
       <c r="E13" t="n">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="F13" t="n">
         <v>200000</v>
       </c>
       <c r="G13" t="n">
-        <v>0.882872</v>
+        <v>0.526682</v>
       </c>
       <c r="H13" t="n">
-        <v>0.867574</v>
+        <v>0.561881</v>
       </c>
       <c r="I13" t="n">
-        <v>0.875156</v>
+        <v>0.543713</v>
       </c>
       <c r="J13" t="n">
-        <v>0.096939</v>
+        <v>0.251314</v>
       </c>
       <c r="K13" t="n">
-        <v>0.875676</v>
+        <v>0.497717</v>
       </c>
       <c r="L13" t="n">
-        <v>0.835052</v>
+        <v>0.561856</v>
       </c>
       <c r="M13" t="n">
-        <v>0.854881</v>
+        <v>0.527845</v>
       </c>
       <c r="N13" t="n">
         <v>0.2</v>
@@ -1763,28 +1763,28 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>_4_15_1_1790733486_11.txt</t>
+          <t>_4_5_5_5_1_1790733545_3.txt</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[5, 5, 5]</t>
         </is>
       </c>
       <c r="Z13" t="n">
         <v>15</v>
       </c>
       <c r="AA13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
         <v>0.1</v>
       </c>
       <c r="B14" t="n">
-        <v>0.112888</v>
+        <v>0.115343</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1810,25 +1810,25 @@
         <v>200000</v>
       </c>
       <c r="G14" t="n">
-        <v>0.832321</v>
+        <v>0.834741</v>
       </c>
       <c r="H14" t="n">
-        <v>0.847772</v>
+        <v>0.856436</v>
       </c>
       <c r="I14" t="n">
-        <v>0.839975</v>
+        <v>0.845449</v>
       </c>
       <c r="J14" t="n">
-        <v>0.126444</v>
+        <v>0.124832</v>
       </c>
       <c r="K14" t="n">
-        <v>0.801047</v>
+        <v>0.787129</v>
       </c>
       <c r="L14" t="n">
-        <v>0.78866</v>
+        <v>0.819588</v>
       </c>
       <c r="M14" t="n">
-        <v>0.794805</v>
+        <v>0.80303</v>
       </c>
       <c r="N14" t="n">
         <v>0.2</v>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>_4_15_1_1790733486_14.txt</t>
+          <t>_4_15_1_1790733486_8.txt</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -1894,42 +1894,42 @@
         <v>0.1</v>
       </c>
       <c r="B15" t="n">
-        <v>0.24956</v>
+        <v>0.113256</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_</t>
+          <t>_4_15_1_</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1790733545</v>
+        <v>1790733486</v>
       </c>
       <c r="E15" t="n">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="F15" t="n">
         <v>200000</v>
       </c>
       <c r="G15" t="n">
-        <v>0.517274</v>
+        <v>0.833132</v>
       </c>
       <c r="H15" t="n">
-        <v>0.667079</v>
+        <v>0.852723</v>
       </c>
       <c r="I15" t="n">
-        <v>0.582703</v>
+        <v>0.842813</v>
       </c>
       <c r="J15" t="n">
-        <v>0.25055</v>
+        <v>0.123418</v>
       </c>
       <c r="K15" t="n">
-        <v>0.463878</v>
+        <v>0.815385</v>
       </c>
       <c r="L15" t="n">
-        <v>0.628866</v>
+        <v>0.819588</v>
       </c>
       <c r="M15" t="n">
-        <v>0.533917</v>
+        <v>0.817481</v>
       </c>
       <c r="N15" t="n">
         <v>0.2</v>
@@ -1965,23 +1965,23 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_1790733545_19.txt</t>
+          <t>_4_15_1_1790733486_16.txt</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>[5, 5, 5]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z15" t="n">
         <v>15</v>
       </c>
       <c r="AA15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -1995,42 +1995,42 @@
         <v>0.1</v>
       </c>
       <c r="B16" t="n">
-        <v>0.102957</v>
+        <v>0.249318</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>_4_15_1_</t>
+          <t>_4_5_5_5_1_</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1790733486</v>
+        <v>1790733545</v>
       </c>
       <c r="E16" t="n">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="F16" t="n">
         <v>200000</v>
       </c>
       <c r="G16" t="n">
-        <v>0.879459</v>
+        <v>0.523973</v>
       </c>
       <c r="H16" t="n">
-        <v>0.884901</v>
+        <v>0.568069</v>
       </c>
       <c r="I16" t="n">
-        <v>0.882172</v>
+        <v>0.545131</v>
       </c>
       <c r="J16" t="n">
-        <v>0.102972</v>
+        <v>0.251479</v>
       </c>
       <c r="K16" t="n">
-        <v>0.867021</v>
+        <v>0.482609</v>
       </c>
       <c r="L16" t="n">
-        <v>0.840206</v>
+        <v>0.572165</v>
       </c>
       <c r="M16" t="n">
-        <v>0.853403</v>
+        <v>0.523585</v>
       </c>
       <c r="N16" t="n">
         <v>0.2</v>
@@ -2066,23 +2066,23 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>_4_15_1_1790733486_5.txt</t>
+          <t>_4_5_5_5_1_1790733545_1.txt</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[5, 5, 5]</t>
         </is>
       </c>
       <c r="Z16" t="n">
         <v>15</v>
       </c>
       <c r="AA16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2096,7 +2096,7 @@
         <v>0.1</v>
       </c>
       <c r="B17" t="n">
-        <v>0.249297</v>
+        <v>0.249299</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2113,25 +2113,25 @@
         <v>200000</v>
       </c>
       <c r="G17" t="n">
-        <v>0.52124</v>
+        <v>0.510759</v>
       </c>
       <c r="H17" t="n">
-        <v>0.561881</v>
+        <v>0.558168</v>
       </c>
       <c r="I17" t="n">
-        <v>0.540798</v>
+        <v>0.533412</v>
       </c>
       <c r="J17" t="n">
-        <v>0.251546</v>
+        <v>0.251241</v>
       </c>
       <c r="K17" t="n">
-        <v>0.467249</v>
+        <v>0.454955</v>
       </c>
       <c r="L17" t="n">
-        <v>0.551546</v>
+        <v>0.5206190000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>0.50591</v>
+        <v>0.485577</v>
       </c>
       <c r="N17" t="n">
         <v>0.2</v>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_1790733545_5.txt</t>
+          <t>_4_5_5_5_1_1790733545_4.txt</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2197,7 +2197,7 @@
         <v>0.1</v>
       </c>
       <c r="B18" t="n">
-        <v>0.172735</v>
+        <v>0.11212</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2214,25 +2214,25 @@
         <v>200000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.771739</v>
+        <v>0.837379</v>
       </c>
       <c r="H18" t="n">
-        <v>0.70297</v>
+        <v>0.8539600000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>0.735751</v>
+        <v>0.845588</v>
       </c>
       <c r="J18" t="n">
-        <v>0.168591</v>
+        <v>0.122896</v>
       </c>
       <c r="K18" t="n">
-        <v>0.779006</v>
+        <v>0.807292</v>
       </c>
       <c r="L18" t="n">
-        <v>0.726804</v>
+        <v>0.798969</v>
       </c>
       <c r="M18" t="n">
-        <v>0.752</v>
+        <v>0.803109</v>
       </c>
       <c r="N18" t="n">
         <v>0.2</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>_4_15_1_1790733486_19.txt</t>
+          <t>_4_15_1_1790733486_7.txt</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2298,7 +2298,7 @@
         <v>0.1</v>
       </c>
       <c r="B19" t="n">
-        <v>0.249279</v>
+        <v>0.24976</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2315,25 +2315,25 @@
         <v>200000</v>
       </c>
       <c r="G19" t="n">
-        <v>0.54023</v>
+        <v>0.52194</v>
       </c>
       <c r="H19" t="n">
-        <v>0.639852</v>
+        <v>0.839109</v>
       </c>
       <c r="I19" t="n">
-        <v>0.585836</v>
+        <v>0.6435689999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>0.251298</v>
+        <v>0.250307</v>
       </c>
       <c r="K19" t="n">
-        <v>0.508475</v>
+        <v>0.486068</v>
       </c>
       <c r="L19" t="n">
-        <v>0.618557</v>
+        <v>0.8092780000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>0.55814</v>
+        <v>0.6073499999999999</v>
       </c>
       <c r="N19" t="n">
         <v>0.2</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_1790733545_13.txt</t>
+          <t>_4_5_5_5_1_1790733545_7.txt</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2399,7 +2399,7 @@
         <v>0.1</v>
       </c>
       <c r="B20" t="n">
-        <v>0.07753699999999999</v>
+        <v>0.110606</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2416,25 +2416,25 @@
         <v>200000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.913043</v>
+        <v>0.8394160000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>0.909653</v>
+        <v>0.8539600000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>0.911345</v>
+        <v>0.846626</v>
       </c>
       <c r="J20" t="n">
-        <v>0.086424</v>
+        <v>0.125746</v>
       </c>
       <c r="K20" t="n">
-        <v>0.860104</v>
+        <v>0.8138300000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>0.85567</v>
+        <v>0.78866</v>
       </c>
       <c r="M20" t="n">
-        <v>0.857881</v>
+        <v>0.801047</v>
       </c>
       <c r="N20" t="n">
         <v>0.2</v>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>_4_15_1_1790733486_15.txt</t>
+          <t>_4_15_1_1790733486_4.txt</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2601,42 +2601,42 @@
         <v>0.1</v>
       </c>
       <c r="B22" t="n">
-        <v>0.074527</v>
+        <v>0.249297</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>_4_15_1_</t>
+          <t>_4_5_5_5_1_</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1790733486</v>
+        <v>1790733545</v>
       </c>
       <c r="E22" t="n">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="F22" t="n">
         <v>200000</v>
       </c>
       <c r="G22" t="n">
-        <v>0.916359</v>
+        <v>0.52124</v>
       </c>
       <c r="H22" t="n">
-        <v>0.92203</v>
+        <v>0.561881</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9191859999999999</v>
+        <v>0.540798</v>
       </c>
       <c r="J22" t="n">
-        <v>0.076834</v>
+        <v>0.251546</v>
       </c>
       <c r="K22" t="n">
-        <v>0.902564</v>
+        <v>0.467249</v>
       </c>
       <c r="L22" t="n">
-        <v>0.907216</v>
+        <v>0.551546</v>
       </c>
       <c r="M22" t="n">
-        <v>0.904884</v>
+        <v>0.50591</v>
       </c>
       <c r="N22" t="n">
         <v>0.2</v>
@@ -2672,28 +2672,28 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>_4_15_1_1790733486_13.txt</t>
+          <t>_4_5_5_5_1_1790733545_5.txt</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[5, 5, 5]</t>
         </is>
       </c>
       <c r="Z22" t="n">
         <v>15</v>
       </c>
       <c r="AA22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2702,42 +2702,42 @@
         <v>0.1</v>
       </c>
       <c r="B23" t="n">
-        <v>0.07781100000000001</v>
+        <v>0.249449</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>_4_15_1_</t>
+          <t>_4_5_5_5_1_</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1790733486</v>
+        <v>1790733545</v>
       </c>
       <c r="E23" t="n">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="F23" t="n">
         <v>200000</v>
       </c>
       <c r="G23" t="n">
-        <v>0.919598</v>
+        <v>0.522326</v>
       </c>
       <c r="H23" t="n">
-        <v>0.905941</v>
+        <v>0.622525</v>
       </c>
       <c r="I23" t="n">
-        <v>0.912718</v>
+        <v>0.568041</v>
       </c>
       <c r="J23" t="n">
-        <v>0.081917</v>
+        <v>0.250687</v>
       </c>
       <c r="K23" t="n">
-        <v>0.871287</v>
+        <v>0.487603</v>
       </c>
       <c r="L23" t="n">
-        <v>0.907216</v>
+        <v>0.608247</v>
       </c>
       <c r="M23" t="n">
-        <v>0.888889</v>
+        <v>0.541284</v>
       </c>
       <c r="N23" t="n">
         <v>0.2</v>
@@ -2773,28 +2773,28 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>_4_15_1_1790733486_3.txt</t>
+          <t>_4_5_5_5_1_1790733545_15.txt</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[5, 5, 5]</t>
         </is>
       </c>
       <c r="Z23" t="n">
         <v>15</v>
       </c>
       <c r="AA23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2803,42 +2803,42 @@
         <v>0.1</v>
       </c>
       <c r="B24" t="n">
-        <v>0.249276</v>
+        <v>0.07753699999999999</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_</t>
+          <t>_4_15_1_</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1790733545</v>
+        <v>1790733486</v>
       </c>
       <c r="E24" t="n">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="F24" t="n">
         <v>200000</v>
       </c>
       <c r="G24" t="n">
-        <v>0.526682</v>
+        <v>0.913043</v>
       </c>
       <c r="H24" t="n">
-        <v>0.561881</v>
+        <v>0.909653</v>
       </c>
       <c r="I24" t="n">
-        <v>0.543713</v>
+        <v>0.911345</v>
       </c>
       <c r="J24" t="n">
-        <v>0.251314</v>
+        <v>0.086424</v>
       </c>
       <c r="K24" t="n">
-        <v>0.497717</v>
+        <v>0.860104</v>
       </c>
       <c r="L24" t="n">
-        <v>0.561856</v>
+        <v>0.85567</v>
       </c>
       <c r="M24" t="n">
-        <v>0.527845</v>
+        <v>0.857881</v>
       </c>
       <c r="N24" t="n">
         <v>0.2</v>
@@ -2874,28 +2874,28 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_1790733545_3.txt</t>
+          <t>_4_15_1_1790733486_15.txt</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>[5, 5, 5]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z24" t="n">
         <v>15</v>
       </c>
       <c r="AA24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
     </row>
@@ -2904,42 +2904,42 @@
         <v>0.1</v>
       </c>
       <c r="B25" t="n">
-        <v>0.24976</v>
+        <v>0.10992</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_</t>
+          <t>_4_15_1_</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1790733545</v>
+        <v>1790733486</v>
       </c>
       <c r="E25" t="n">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="F25" t="n">
         <v>200000</v>
       </c>
       <c r="G25" t="n">
-        <v>0.52194</v>
+        <v>0.8434469999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>0.839109</v>
+        <v>0.860148</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6435689999999999</v>
+        <v>0.851716</v>
       </c>
       <c r="J25" t="n">
-        <v>0.250307</v>
+        <v>0.122324</v>
       </c>
       <c r="K25" t="n">
-        <v>0.486068</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>0.8092780000000001</v>
+        <v>0.835052</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6073499999999999</v>
+        <v>0.822335</v>
       </c>
       <c r="N25" t="n">
         <v>0.2</v>
@@ -2975,23 +2975,23 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_1790733545_7.txt</t>
+          <t>_4_15_1_1790733486_12.txt</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>[5, 5, 5]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z25" t="n">
         <v>15</v>
       </c>
       <c r="AA25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3005,7 +3005,7 @@
         <v>0.1</v>
       </c>
       <c r="B26" t="n">
-        <v>0.249299</v>
+        <v>0.249334</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3022,25 +3022,25 @@
         <v>200000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.518112</v>
+        <v>0.524176</v>
       </c>
       <c r="H26" t="n">
-        <v>0.584158</v>
+        <v>0.590347</v>
       </c>
       <c r="I26" t="n">
-        <v>0.549156</v>
+        <v>0.555297</v>
       </c>
       <c r="J26" t="n">
-        <v>0.251625</v>
+        <v>0.251574</v>
       </c>
       <c r="K26" t="n">
-        <v>0.478814</v>
+        <v>0.487179</v>
       </c>
       <c r="L26" t="n">
-        <v>0.582474</v>
+        <v>0.587629</v>
       </c>
       <c r="M26" t="n">
-        <v>0.525581</v>
+        <v>0.53271</v>
       </c>
       <c r="N26" t="n">
         <v>0.2</v>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_1790733545_6.txt</t>
+          <t>_4_5_5_5_1_1790733545_0.txt</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3106,42 +3106,42 @@
         <v>0.1</v>
       </c>
       <c r="B27" t="n">
-        <v>0.07828499999999999</v>
+        <v>0.248735</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>_4_15_1_</t>
+          <t>_4_5_5_5_1_</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1790733486</v>
+        <v>1790733545</v>
       </c>
       <c r="E27" t="n">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="F27" t="n">
         <v>200000</v>
       </c>
       <c r="G27" t="n">
-        <v>0.905119</v>
+        <v>0.541393</v>
       </c>
       <c r="H27" t="n">
-        <v>0.897277</v>
+        <v>0.509901</v>
       </c>
       <c r="I27" t="n">
-        <v>0.901181</v>
+        <v>0.5251749999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>0.08906699999999999</v>
+        <v>0.250957</v>
       </c>
       <c r="K27" t="n">
-        <v>0.854271</v>
+        <v>0.47449</v>
       </c>
       <c r="L27" t="n">
-        <v>0.876289</v>
+        <v>0.479381</v>
       </c>
       <c r="M27" t="n">
-        <v>0.86514</v>
+        <v>0.476923</v>
       </c>
       <c r="N27" t="n">
         <v>0.2</v>
@@ -3177,28 +3177,28 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>_4_15_1_1790733486_2.txt</t>
+          <t>_4_5_5_5_1_1790733545_11.txt</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[5, 5, 5]</t>
         </is>
       </c>
       <c r="Z27" t="n">
         <v>15</v>
       </c>
       <c r="AA27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
         <v>0.1</v>
       </c>
       <c r="B28" t="n">
-        <v>0.249327</v>
+        <v>0.249191</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3224,25 +3224,25 @@
         <v>200000</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5213</v>
+        <v>0.525444</v>
       </c>
       <c r="H28" t="n">
-        <v>0.575495</v>
+        <v>0.549505</v>
       </c>
       <c r="I28" t="n">
-        <v>0.547059</v>
+        <v>0.537205</v>
       </c>
       <c r="J28" t="n">
-        <v>0.251511</v>
+        <v>0.251386</v>
       </c>
       <c r="K28" t="n">
-        <v>0.480519</v>
+        <v>0.477273</v>
       </c>
       <c r="L28" t="n">
-        <v>0.572165</v>
+        <v>0.541237</v>
       </c>
       <c r="M28" t="n">
-        <v>0.522353</v>
+        <v>0.507246</v>
       </c>
       <c r="N28" t="n">
         <v>0.2</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_1790733545_14.txt</t>
+          <t>_4_5_5_5_1_1790733545_8.txt</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3308,42 +3308,42 @@
         <v>0.1</v>
       </c>
       <c r="B29" t="n">
-        <v>0.249295</v>
+        <v>0.09510200000000001</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_</t>
+          <t>_4_15_1_</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1790733545</v>
+        <v>1790733486</v>
       </c>
       <c r="E29" t="n">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="F29" t="n">
         <v>200000</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5252869999999999</v>
+        <v>0.881841</v>
       </c>
       <c r="H29" t="n">
-        <v>0.565594</v>
+        <v>0.877475</v>
       </c>
       <c r="I29" t="n">
-        <v>0.544696</v>
+        <v>0.879653</v>
       </c>
       <c r="J29" t="n">
-        <v>0.251227</v>
+        <v>0.104068</v>
       </c>
       <c r="K29" t="n">
-        <v>0.502283</v>
+        <v>0.854167</v>
       </c>
       <c r="L29" t="n">
-        <v>0.56701</v>
+        <v>0.845361</v>
       </c>
       <c r="M29" t="n">
-        <v>0.5326880000000001</v>
+        <v>0.849741</v>
       </c>
       <c r="N29" t="n">
         <v>0.2</v>
@@ -3379,28 +3379,28 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_1790733545_16.txt</t>
+          <t>_4_15_1_1790733486_17.txt</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>[5, 5, 5]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z29" t="n">
         <v>15</v>
       </c>
       <c r="AA29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>0.1</v>
       </c>
       <c r="B30" t="n">
-        <v>0.249318</v>
+        <v>0.249313</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3426,25 +3426,25 @@
         <v>200000</v>
       </c>
       <c r="G30" t="n">
-        <v>0.523973</v>
+        <v>0.530405</v>
       </c>
       <c r="H30" t="n">
-        <v>0.568069</v>
+        <v>0.582921</v>
       </c>
       <c r="I30" t="n">
-        <v>0.545131</v>
+        <v>0.5554249999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>0.251479</v>
+        <v>0.251387</v>
       </c>
       <c r="K30" t="n">
-        <v>0.482609</v>
+        <v>0.493333</v>
       </c>
       <c r="L30" t="n">
         <v>0.572165</v>
       </c>
       <c r="M30" t="n">
-        <v>0.523585</v>
+        <v>0.529833</v>
       </c>
       <c r="N30" t="n">
         <v>0.2</v>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_1790733545_1.txt</t>
+          <t>_4_5_5_5_1_1790733545_10.txt</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3510,42 +3510,42 @@
         <v>0.1</v>
       </c>
       <c r="B31" t="n">
-        <v>0.249449</v>
+        <v>0.07781100000000001</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_</t>
+          <t>_4_15_1_</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1790733545</v>
+        <v>1790733486</v>
       </c>
       <c r="E31" t="n">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="F31" t="n">
         <v>200000</v>
       </c>
       <c r="G31" t="n">
-        <v>0.522326</v>
+        <v>0.919598</v>
       </c>
       <c r="H31" t="n">
-        <v>0.622525</v>
+        <v>0.905941</v>
       </c>
       <c r="I31" t="n">
-        <v>0.568041</v>
+        <v>0.912718</v>
       </c>
       <c r="J31" t="n">
-        <v>0.250687</v>
+        <v>0.081917</v>
       </c>
       <c r="K31" t="n">
-        <v>0.487603</v>
+        <v>0.871287</v>
       </c>
       <c r="L31" t="n">
-        <v>0.608247</v>
+        <v>0.907216</v>
       </c>
       <c r="M31" t="n">
-        <v>0.541284</v>
+        <v>0.888889</v>
       </c>
       <c r="N31" t="n">
         <v>0.2</v>
@@ -3581,28 +3581,28 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_1790733545_15.txt</t>
+          <t>_4_15_1_1790733486_3.txt</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>[5, 5, 5]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z31" t="n">
         <v>15</v>
       </c>
       <c r="AA31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
     </row>
@@ -3611,42 +3611,42 @@
         <v>0.1</v>
       </c>
       <c r="B32" t="n">
-        <v>0.249313</v>
+        <v>0.07584399999999999</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_</t>
+          <t>_4_15_1_</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1790733545</v>
+        <v>1790733486</v>
       </c>
       <c r="E32" t="n">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="F32" t="n">
         <v>200000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.530405</v>
+        <v>0.91</v>
       </c>
       <c r="H32" t="n">
-        <v>0.582921</v>
+        <v>0.90099</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5554249999999999</v>
+        <v>0.905473</v>
       </c>
       <c r="J32" t="n">
-        <v>0.251387</v>
+        <v>0.086714</v>
       </c>
       <c r="K32" t="n">
-        <v>0.493333</v>
+        <v>0.875</v>
       </c>
       <c r="L32" t="n">
-        <v>0.572165</v>
+        <v>0.8659790000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>0.529833</v>
+        <v>0.870466</v>
       </c>
       <c r="N32" t="n">
         <v>0.2</v>
@@ -3682,28 +3682,28 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_1790733545_10.txt</t>
+          <t>_4_15_1_1790733486_9.txt</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>[5, 5, 5]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z32" t="n">
         <v>15</v>
       </c>
       <c r="AA32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
     </row>
@@ -3712,42 +3712,42 @@
         <v>0.1</v>
       </c>
       <c r="B33" t="n">
-        <v>0.248735</v>
+        <v>0.077861</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_</t>
+          <t>_4_15_1_</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1790733545</v>
+        <v>1790733486</v>
       </c>
       <c r="E33" t="n">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="F33" t="n">
         <v>200000</v>
       </c>
       <c r="G33" t="n">
-        <v>0.541393</v>
+        <v>0.91</v>
       </c>
       <c r="H33" t="n">
-        <v>0.509901</v>
+        <v>0.90099</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5251749999999999</v>
+        <v>0.905473</v>
       </c>
       <c r="J33" t="n">
-        <v>0.250957</v>
+        <v>0.084911</v>
       </c>
       <c r="K33" t="n">
-        <v>0.47449</v>
+        <v>0.891753</v>
       </c>
       <c r="L33" t="n">
-        <v>0.479381</v>
+        <v>0.891753</v>
       </c>
       <c r="M33" t="n">
-        <v>0.476923</v>
+        <v>0.891753</v>
       </c>
       <c r="N33" t="n">
         <v>0.2</v>
@@ -3783,28 +3783,28 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_1790733545_11.txt</t>
+          <t>_4_15_1_1790733486_10.txt</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>[5, 5, 5]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z33" t="n">
         <v>15</v>
       </c>
       <c r="AA33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3813,7 @@
         <v>0.1</v>
       </c>
       <c r="B34" t="n">
-        <v>0.086337</v>
+        <v>0.112888</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3830,25 +3830,25 @@
         <v>200000</v>
       </c>
       <c r="G34" t="n">
-        <v>0.922179</v>
+        <v>0.832321</v>
       </c>
       <c r="H34" t="n">
-        <v>0.879951</v>
+        <v>0.847772</v>
       </c>
       <c r="I34" t="n">
-        <v>0.90057</v>
+        <v>0.839975</v>
       </c>
       <c r="J34" t="n">
-        <v>0.084504</v>
+        <v>0.126444</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9297299999999999</v>
+        <v>0.801047</v>
       </c>
       <c r="L34" t="n">
-        <v>0.886598</v>
+        <v>0.78866</v>
       </c>
       <c r="M34" t="n">
-        <v>0.907652</v>
+        <v>0.794805</v>
       </c>
       <c r="N34" t="n">
         <v>0.2</v>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>_4_15_1_1790733486_6.txt</t>
+          <t>_4_15_1_1790733486_14.txt</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3914,42 +3914,42 @@
         <v>0.1</v>
       </c>
       <c r="B35" t="n">
-        <v>0.24934</v>
+        <v>0.074527</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_</t>
+          <t>_4_15_1_</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1790733545</v>
+        <v>1790733486</v>
       </c>
       <c r="E35" t="n">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="F35" t="n">
         <v>200000</v>
       </c>
       <c r="G35" t="n">
-        <v>0.521542</v>
+        <v>0.916359</v>
       </c>
       <c r="H35" t="n">
-        <v>0.569307</v>
+        <v>0.92203</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5443789999999999</v>
+        <v>0.9191859999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>0.251394</v>
+        <v>0.076834</v>
       </c>
       <c r="K35" t="n">
-        <v>0.482456</v>
+        <v>0.902564</v>
       </c>
       <c r="L35" t="n">
-        <v>0.56701</v>
+        <v>0.907216</v>
       </c>
       <c r="M35" t="n">
-        <v>0.521327</v>
+        <v>0.904884</v>
       </c>
       <c r="N35" t="n">
         <v>0.2</v>
@@ -3985,28 +3985,28 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_1790733545_12.txt</t>
+          <t>_4_15_1_1790733486_13.txt</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>[5, 5, 5]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z35" t="n">
         <v>15</v>
       </c>
       <c r="AA35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4015,7 @@
         <v>0.1</v>
       </c>
       <c r="B36" t="n">
-        <v>0.11212</v>
+        <v>0.09222</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4032,25 +4032,25 @@
         <v>200000</v>
       </c>
       <c r="G36" t="n">
-        <v>0.837379</v>
+        <v>0.89196</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8539600000000001</v>
+        <v>0.878713</v>
       </c>
       <c r="I36" t="n">
-        <v>0.845588</v>
+        <v>0.885287</v>
       </c>
       <c r="J36" t="n">
-        <v>0.122896</v>
+        <v>0.100506</v>
       </c>
       <c r="K36" t="n">
-        <v>0.807292</v>
+        <v>0.880208</v>
       </c>
       <c r="L36" t="n">
-        <v>0.798969</v>
+        <v>0.871134</v>
       </c>
       <c r="M36" t="n">
-        <v>0.803109</v>
+        <v>0.875648</v>
       </c>
       <c r="N36" t="n">
         <v>0.2</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>_4_15_1_1790733486_7.txt</t>
+          <t>_4_15_1_1790733486_0.txt</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
         <v>0.1</v>
       </c>
       <c r="B37" t="n">
-        <v>0.249299</v>
+        <v>0.249327</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4133,25 +4133,25 @@
         <v>200000</v>
       </c>
       <c r="G37" t="n">
-        <v>0.510759</v>
+        <v>0.5213</v>
       </c>
       <c r="H37" t="n">
-        <v>0.558168</v>
+        <v>0.575495</v>
       </c>
       <c r="I37" t="n">
-        <v>0.533412</v>
+        <v>0.547059</v>
       </c>
       <c r="J37" t="n">
-        <v>0.251241</v>
+        <v>0.251511</v>
       </c>
       <c r="K37" t="n">
-        <v>0.454955</v>
+        <v>0.480519</v>
       </c>
       <c r="L37" t="n">
-        <v>0.5206190000000001</v>
+        <v>0.572165</v>
       </c>
       <c r="M37" t="n">
-        <v>0.485577</v>
+        <v>0.522353</v>
       </c>
       <c r="N37" t="n">
         <v>0.2</v>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_1790733545_4.txt</t>
+          <t>_4_5_5_5_1_1790733545_14.txt</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4217,7 +4217,7 @@
         <v>0.1</v>
       </c>
       <c r="B38" t="n">
-        <v>0.07584399999999999</v>
+        <v>0.151501</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4234,25 +4234,25 @@
         <v>200000</v>
       </c>
       <c r="G38" t="n">
-        <v>0.91</v>
+        <v>0.787286</v>
       </c>
       <c r="H38" t="n">
-        <v>0.90099</v>
+        <v>0.79703</v>
       </c>
       <c r="I38" t="n">
-        <v>0.905473</v>
+        <v>0.7921280000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>0.086714</v>
+        <v>0.151953</v>
       </c>
       <c r="K38" t="n">
-        <v>0.875</v>
+        <v>0.782828</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8659790000000001</v>
+        <v>0.798969</v>
       </c>
       <c r="M38" t="n">
-        <v>0.870466</v>
+        <v>0.790816</v>
       </c>
       <c r="N38" t="n">
         <v>0.2</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>_4_15_1_1790733486_9.txt</t>
+          <t>_4_15_1_1790733486_1.txt</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4318,42 +4318,42 @@
         <v>0.1</v>
       </c>
       <c r="B39" t="n">
-        <v>0.151501</v>
+        <v>0.249299</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>_4_15_1_</t>
+          <t>_4_5_5_5_1_</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1790733486</v>
+        <v>1790733545</v>
       </c>
       <c r="E39" t="n">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="F39" t="n">
         <v>200000</v>
       </c>
       <c r="G39" t="n">
-        <v>0.787286</v>
+        <v>0.518112</v>
       </c>
       <c r="H39" t="n">
-        <v>0.79703</v>
+        <v>0.584158</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7921280000000001</v>
+        <v>0.549156</v>
       </c>
       <c r="J39" t="n">
-        <v>0.151953</v>
+        <v>0.251625</v>
       </c>
       <c r="K39" t="n">
-        <v>0.782828</v>
+        <v>0.478814</v>
       </c>
       <c r="L39" t="n">
-        <v>0.798969</v>
+        <v>0.582474</v>
       </c>
       <c r="M39" t="n">
-        <v>0.790816</v>
+        <v>0.525581</v>
       </c>
       <c r="N39" t="n">
         <v>0.2</v>
@@ -4389,23 +4389,23 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>_4_15_1_1790733486_1.txt</t>
+          <t>_4_5_5_5_1_1790733545_6.txt</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[5, 5, 5]</t>
         </is>
       </c>
       <c r="Z39" t="n">
         <v>15</v>
       </c>
       <c r="AA39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4419,7 +4419,7 @@
         <v>0.1</v>
       </c>
       <c r="B40" t="n">
-        <v>0.249191</v>
+        <v>0.249549</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4436,25 +4436,25 @@
         <v>200000</v>
       </c>
       <c r="G40" t="n">
-        <v>0.525444</v>
+        <v>0.539583</v>
       </c>
       <c r="H40" t="n">
-        <v>0.549505</v>
+        <v>0.641089</v>
       </c>
       <c r="I40" t="n">
-        <v>0.537205</v>
+        <v>0.585973</v>
       </c>
       <c r="J40" t="n">
-        <v>0.251386</v>
+        <v>0.250611</v>
       </c>
       <c r="K40" t="n">
-        <v>0.477273</v>
+        <v>0.5375</v>
       </c>
       <c r="L40" t="n">
-        <v>0.541237</v>
+        <v>0.664948</v>
       </c>
       <c r="M40" t="n">
-        <v>0.507246</v>
+        <v>0.5944700000000001</v>
       </c>
       <c r="N40" t="n">
         <v>0.2</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_1790733545_8.txt</t>
+          <t>_4_5_5_5_1_1790733545_18.txt</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4520,42 +4520,42 @@
         <v>0.1</v>
       </c>
       <c r="B41" t="n">
-        <v>0.249549</v>
+        <v>0.102957</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_</t>
+          <t>_4_15_1_</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1790733545</v>
+        <v>1790733486</v>
       </c>
       <c r="E41" t="n">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="F41" t="n">
         <v>200000</v>
       </c>
       <c r="G41" t="n">
-        <v>0.539583</v>
+        <v>0.879459</v>
       </c>
       <c r="H41" t="n">
-        <v>0.641089</v>
+        <v>0.884901</v>
       </c>
       <c r="I41" t="n">
-        <v>0.585973</v>
+        <v>0.882172</v>
       </c>
       <c r="J41" t="n">
-        <v>0.250611</v>
+        <v>0.102972</v>
       </c>
       <c r="K41" t="n">
-        <v>0.5375</v>
+        <v>0.867021</v>
       </c>
       <c r="L41" t="n">
-        <v>0.664948</v>
+        <v>0.840206</v>
       </c>
       <c r="M41" t="n">
-        <v>0.5944700000000001</v>
+        <v>0.853403</v>
       </c>
       <c r="N41" t="n">
         <v>0.2</v>
@@ -4591,23 +4591,23 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>_4_5_5_5_1_1790733545_18.txt</t>
+          <t>_4_15_1_1790733486_5.txt</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>[5, 5, 5]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z41" t="n">
         <v>15</v>
       </c>
       <c r="AA41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -4682,7 +4682,7 @@
         <v>0.8427738</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04275294555269357</v>
+        <v>0.04275294555269355</v>
       </c>
       <c r="D2" t="n">
         <v>0.907652</v>
@@ -4710,7 +4710,7 @@
         <v>0.5270534</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03257881625648306</v>
+        <v>0.03257881625648303</v>
       </c>
       <c r="D3" t="n">
         <v>0.6073499999999999</v>
